--- a/data/raw_lab_data/TOC_Analysis_Fuhrberg.xlsx
+++ b/data/raw_lab_data/TOC_Analysis_Fuhrberg.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/johannholdt/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vcant\Documents\ffa_colexperiment\data\raw_lab_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{39315B98-1568-0346-8221-542CECC3881C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D726EF7-93AC-46D2-84AC-78DA1766AC82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1240" yWindow="1780" windowWidth="41280" windowHeight="23160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -78,13 +78,7 @@
     <t>C1-4-8</t>
   </si>
   <si>
-    <t>Br17-18</t>
-  </si>
-  <si>
     <t>C4-4-8</t>
-  </si>
-  <si>
-    <t>Br-17-18_2</t>
   </si>
   <si>
     <t>C3-4-8</t>
@@ -98,15 +92,21 @@
   <si>
     <t>Br16-18-19_2</t>
   </si>
+  <si>
+    <t>Br 17-18</t>
+  </si>
+  <si>
+    <t>Br 17-18_2</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -705,7 +705,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -721,9 +721,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -744,22 +741,22 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="33" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="33" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="33" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="33" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="33" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="33" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1108,22 +1105,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L120"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.1640625" customWidth="1"/>
-    <col min="3" max="3" width="13.83203125" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" style="2"/>
-    <col min="6" max="6" width="14.33203125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="18.33203125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.5" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" style="2"/>
+    <col min="6" max="6" width="14.28515625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="24.83203125" customWidth="1"/>
-    <col min="11" max="11" width="24.6640625" customWidth="1"/>
-    <col min="12" max="12" width="21.6640625" customWidth="1"/>
+    <col min="10" max="10" width="24.85546875" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" customWidth="1"/>
+    <col min="12" max="12" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="26.1" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1155,9 +1152,9 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
     </row>
-    <row r="2" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
+    <row r="2" spans="1:12" ht="15.75" thickBot="1"/>
+    <row r="3" spans="1:12">
+      <c r="A3" s="10" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="6">
@@ -1172,262 +1169,262 @@
       <c r="E3" s="6">
         <v>11.992000000000001</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="13">
         <v>1.89E-2</v>
       </c>
-      <c r="G3" s="15">
+      <c r="G3" s="14">
         <v>11.973000000000001</v>
       </c>
       <c r="H3" s="5"/>
-      <c r="I3" s="9">
+      <c r="I3" s="8">
         <v>46051.481423611112</v>
       </c>
-      <c r="J3" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="12" t="s">
+      <c r="J3" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="5">
         <v>4.163E-2</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="5">
         <v>15668703</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="5">
         <v>0.71762999999999999</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="5">
         <v>12.013999999999999</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="15">
         <v>1.8100000000000002E-2</v>
       </c>
-      <c r="G4" s="17">
+      <c r="G4" s="16">
         <v>11.996</v>
       </c>
       <c r="H4" s="5"/>
-      <c r="I4" s="9">
+      <c r="I4" s="8">
         <v>46051.50309027778</v>
       </c>
-      <c r="J4" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
+      <c r="J4" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="5">
         <v>2.971E-2</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="5">
         <v>11153789</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="5">
         <v>0.51083999999999996</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="5">
         <v>11.984</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="15">
         <v>1.46E-2</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="16">
         <v>11.968999999999999</v>
       </c>
       <c r="H5" s="5"/>
-      <c r="I5" s="9">
+      <c r="I5" s="8">
         <v>46051.524525462963</v>
       </c>
-      <c r="J5" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
+      <c r="J5" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="5">
         <v>5.0959999999999998E-2</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="5">
         <v>7984499</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="5">
         <v>0.36569000000000002</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="5">
         <v>5.0012999999999996</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="15">
         <v>2.2100000000000002E-2</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="16">
         <v>4.9793000000000003</v>
       </c>
       <c r="H6" s="5"/>
-      <c r="I6" s="9">
+      <c r="I6" s="8">
         <v>46051.54619212963</v>
       </c>
-      <c r="J6" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
+      <c r="J6" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="5">
         <v>4.2220000000000001E-2</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="5">
         <v>6610670</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="5">
         <v>0.30276999999999998</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="5">
         <v>4.9980000000000002</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="15">
         <v>2.7199999999999998E-2</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="16">
         <v>4.9707999999999997</v>
       </c>
       <c r="H7" s="5"/>
-      <c r="I7" s="9">
+      <c r="I7" s="8">
         <v>46051.56763888889</v>
       </c>
-      <c r="J7" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
+      <c r="J7" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="5">
         <v>2.9100000000000001E-2</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="5">
         <v>4545813</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="5">
         <v>0.2082</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="5">
         <v>4.9863999999999997</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="15">
         <v>3.0499999999999999E-2</v>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="16">
         <v>4.9558999999999997</v>
       </c>
       <c r="H8" s="5"/>
-      <c r="I8" s="9">
+      <c r="I8" s="8">
         <v>46051.589305555557</v>
       </c>
-      <c r="J8" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
+      <c r="J8" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="5">
         <v>3.1559999999999998E-2</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="5">
         <v>1009252</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="5">
         <v>4.6224000000000001E-2</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="5">
         <v>1.0207999999999999</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="15">
         <v>2.8400000000000002E-2</v>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="16">
         <v>0.99239999999999995</v>
       </c>
       <c r="H9" s="5"/>
-      <c r="I9" s="9">
+      <c r="I9" s="8">
         <v>46051.610717592594</v>
       </c>
-      <c r="J9" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
+      <c r="J9" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="5">
         <v>4.163E-2</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="5">
         <v>1330924</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="5">
         <v>6.0956000000000003E-2</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="5">
         <v>1.0205</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="15">
         <v>2.4E-2</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="16">
         <v>0.99650000000000005</v>
       </c>
       <c r="H10" s="5"/>
-      <c r="I10" s="9">
+      <c r="I10" s="8">
         <v>46051.632372685184</v>
       </c>
-      <c r="J10" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="J10" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A11" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="7">
         <v>4.9500000000000002E-2</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <v>1606209</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="7">
         <v>7.3564000000000004E-2</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="7">
         <v>1.0358000000000001</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="17">
         <v>2.81E-2</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="18">
         <v>1.0077</v>
       </c>
       <c r="H11" s="5"/>
-      <c r="I11" s="9">
+      <c r="I11" s="8">
         <v>46051.653807870367</v>
       </c>
-      <c r="J11" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
+      <c r="J11" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="10" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="6">
@@ -1442,52 +1439,52 @@
       <c r="E12" s="6">
         <v>0.25431999999999999</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="13">
         <v>0.15</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="14">
         <v>0.1043</v>
       </c>
       <c r="H12" s="5"/>
-      <c r="I12" s="9">
+      <c r="I12" s="8">
         <v>46051.675462962965</v>
       </c>
-      <c r="J12" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="J12" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A13" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="7">
         <v>0.26985999999999999</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="7">
         <v>2178821</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="7">
         <v>9.9790000000000004E-2</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="7">
         <v>0.25774000000000002</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="17">
         <v>0.156</v>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="18">
         <v>0.1018</v>
       </c>
       <c r="H13" s="5"/>
-      <c r="I13" s="9">
+      <c r="I13" s="8">
         <v>46051.696898148148</v>
       </c>
-      <c r="J13" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
+      <c r="J13" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="6">
@@ -1502,52 +1499,52 @@
       <c r="E14" s="6">
         <v>0.11438</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="13">
         <v>7.4300000000000005E-2</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="14">
         <v>0.04</v>
       </c>
       <c r="H14" s="5"/>
-      <c r="I14" s="9">
+      <c r="I14" s="8">
         <v>46051.718553240738</v>
       </c>
-      <c r="J14" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
+      <c r="J14" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A15" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="7">
         <v>0.22466</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="7">
         <v>814377</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="7">
         <v>3.7297999999999998E-2</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="7">
         <v>0.11572</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="17">
         <v>7.6100000000000001E-2</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="18">
         <v>3.9600000000000003E-2</v>
       </c>
       <c r="H15" s="5"/>
-      <c r="I15" s="9">
+      <c r="I15" s="8">
         <v>46051.739988425928</v>
       </c>
-      <c r="J15" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="11" t="s">
+      <c r="J15" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="10" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="6">
@@ -1562,52 +1559,52 @@
       <c r="E16" s="6">
         <v>0.31911</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="13">
         <v>0.11749999999999999</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="14">
         <v>0.20169999999999999</v>
       </c>
       <c r="H16" s="5"/>
-      <c r="I16" s="9">
+      <c r="I16" s="8">
         <v>46051.761643518519</v>
       </c>
-      <c r="J16" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
+      <c r="J16" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A17" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="7">
         <v>0.24732999999999999</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="7">
         <v>2458652</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="7">
         <v>0.11261</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="7">
         <v>0.31733</v>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="17">
         <v>0.1166</v>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="18">
         <v>0.20080000000000001</v>
       </c>
       <c r="H17" s="5"/>
-      <c r="I17" s="9">
+      <c r="I17" s="8">
         <v>46051.783055555556</v>
       </c>
-      <c r="J17" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
+      <c r="J17" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="10" t="s">
         <v>16</v>
       </c>
       <c r="B18" s="6">
@@ -1622,112 +1619,112 @@
       <c r="E18" s="6">
         <v>0.2077</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="13">
         <v>0.14460000000000001</v>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="14">
         <v>6.3100000000000003E-2</v>
       </c>
       <c r="H18" s="5"/>
-      <c r="I18" s="9">
+      <c r="I18" s="8">
         <v>46051.804710648146</v>
       </c>
-      <c r="J18" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
+      <c r="J18" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A19" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="7">
         <v>0.26758999999999999</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="7">
         <v>1757508</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="7">
         <v>8.0493999999999996E-2</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="7">
         <v>0.20967</v>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="17">
         <v>0.14810000000000001</v>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="18">
         <v>6.1600000000000002E-2</v>
       </c>
       <c r="H19" s="5"/>
-      <c r="I19" s="9">
+      <c r="I19" s="8">
         <v>46051.82613425926</v>
       </c>
-      <c r="J19" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A20" s="12" t="s">
+      <c r="J19" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="5">
         <v>0.25247000000000003</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="5">
         <v>3555756</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="5">
         <v>0.16284999999999999</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="5">
         <v>0.44957999999999998</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="15">
         <v>0.1512</v>
       </c>
-      <c r="G20" s="17">
+      <c r="G20" s="16">
         <v>0.2984</v>
       </c>
       <c r="H20" s="5"/>
-      <c r="I20" s="9">
+      <c r="I20" s="8">
         <v>46051.847662037035</v>
       </c>
-      <c r="J20" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="J20" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A21" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="5">
         <v>0.29877999999999999</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="5">
         <v>4231196</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="5">
         <v>0.19378999999999999</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="5">
         <v>0.45206000000000002</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="15">
         <v>0.15290000000000001</v>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="16">
         <v>0.29920000000000002</v>
       </c>
       <c r="H21" s="5"/>
-      <c r="I21" s="9">
+      <c r="I21" s="8">
         <v>46051.869189814817</v>
       </c>
-      <c r="J21" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A22" s="11" t="s">
+      <c r="J21" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B22" s="6">
@@ -1742,53 +1739,53 @@
       <c r="E22" s="6">
         <v>5.0243000000000002</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="13">
         <v>4.7199999999999999E-2</v>
       </c>
-      <c r="G22" s="15">
+      <c r="G22" s="14">
         <v>4.9771000000000001</v>
       </c>
       <c r="H22" s="5"/>
-      <c r="I22" s="9">
+      <c r="I22" s="8">
         <v>46051.890856481485</v>
       </c>
-      <c r="J22" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
+      <c r="J22" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A23" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="7">
         <v>2.6579999999999999E-2</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="7">
         <v>9999090</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="7">
         <v>0.45795999999999998</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="7">
         <v>12.007999999999999</v>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="17">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="18">
         <v>11.983000000000001</v>
       </c>
       <c r="H23" s="5"/>
-      <c r="I23" s="9">
+      <c r="I23" s="8">
         <v>46051.912303240744</v>
       </c>
-      <c r="J23" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24" s="11" t="s">
-        <v>18</v>
+      <c r="J23" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="B24" s="6">
         <v>0.31880999999999998</v>
@@ -1802,53 +1799,53 @@
       <c r="E24" s="6">
         <v>0.45818999999999999</v>
       </c>
-      <c r="F24" s="14">
+      <c r="F24" s="13">
         <v>0.1153</v>
       </c>
-      <c r="G24" s="15">
+      <c r="G24" s="14">
         <v>0.34289999999999998</v>
       </c>
       <c r="H24" s="5"/>
-      <c r="I24" s="9">
+      <c r="I24" s="8">
         <v>46051.933842592596</v>
       </c>
-      <c r="J24" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
+      <c r="J24" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A25" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="7">
+        <v>0.34673999999999999</v>
+      </c>
+      <c r="C25" s="7">
+        <v>6200571</v>
+      </c>
+      <c r="D25" s="7">
+        <v>0.28399000000000002</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.57082999999999995</v>
+      </c>
+      <c r="F25" s="17">
+        <v>0.1384</v>
+      </c>
+      <c r="G25" s="18">
+        <v>0.43240000000000001</v>
+      </c>
+      <c r="H25" s="5"/>
+      <c r="I25" s="8">
+        <v>46051.955509259256</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="10" t="s">
         <v>18</v>
-      </c>
-      <c r="B25" s="8">
-        <v>0.34673999999999999</v>
-      </c>
-      <c r="C25" s="8">
-        <v>6200571</v>
-      </c>
-      <c r="D25" s="8">
-        <v>0.28399000000000002</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.57082999999999995</v>
-      </c>
-      <c r="F25" s="18">
-        <v>0.1384</v>
-      </c>
-      <c r="G25" s="19">
-        <v>0.43240000000000001</v>
-      </c>
-      <c r="H25" s="5"/>
-      <c r="I25" s="9">
-        <v>46051.955509259256</v>
-      </c>
-      <c r="J25" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" s="11" t="s">
-        <v>19</v>
       </c>
       <c r="B26" s="6">
         <v>0.30235000000000001</v>
@@ -1862,53 +1859,53 @@
       <c r="E26" s="6">
         <v>0.13619999999999999</v>
       </c>
-      <c r="F26" s="14">
+      <c r="F26" s="13">
         <v>8.77E-2</v>
       </c>
-      <c r="G26" s="15">
+      <c r="G26" s="14">
         <v>4.8599999999999997E-2</v>
       </c>
       <c r="H26" s="5"/>
-      <c r="I26" s="9">
+      <c r="I26" s="8">
         <v>46051.976944444446</v>
       </c>
-      <c r="J26" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27" s="8">
+      <c r="J26" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A27" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="7">
         <v>0.33661000000000002</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="7">
         <v>1465900</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="7">
         <v>6.7138000000000003E-2</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="7">
         <v>0.13902</v>
       </c>
-      <c r="F27" s="18">
+      <c r="F27" s="17">
         <v>8.6900000000000005E-2</v>
       </c>
-      <c r="G27" s="19">
+      <c r="G27" s="18">
         <v>5.2200000000000003E-2</v>
       </c>
       <c r="H27" s="5"/>
-      <c r="I27" s="9">
+      <c r="I27" s="8">
         <v>46051.998599537037</v>
       </c>
-      <c r="J27" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A28" s="11" t="s">
-        <v>20</v>
+      <c r="J27" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="B28" s="6">
         <v>0.32012000000000002</v>
@@ -1922,53 +1919,53 @@
       <c r="E28" s="6">
         <v>0.2306</v>
       </c>
-      <c r="F28" s="14">
+      <c r="F28" s="13">
         <v>8.9599999999999999E-2</v>
       </c>
-      <c r="G28" s="15">
+      <c r="G28" s="14">
         <v>0.14099999999999999</v>
       </c>
       <c r="H28" s="5"/>
-      <c r="I28" s="9">
+      <c r="I28" s="8">
         <v>46052.020057870373</v>
       </c>
-      <c r="J28" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B29" s="8">
+      <c r="J28" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A29" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" s="7">
         <v>0.36582999999999999</v>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="7">
         <v>2611013</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="7">
         <v>0.11958000000000001</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="7">
         <v>0.22783999999999999</v>
       </c>
-      <c r="F29" s="18">
+      <c r="F29" s="17">
         <v>8.8499999999999995E-2</v>
       </c>
-      <c r="G29" s="19">
+      <c r="G29" s="18">
         <v>0.13930000000000001</v>
       </c>
       <c r="H29" s="5"/>
-      <c r="I29" s="9">
+      <c r="I29" s="8">
         <v>46052.041712962964</v>
       </c>
-      <c r="J29" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A30" s="11" t="s">
-        <v>21</v>
+      <c r="J29" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="B30" s="6">
         <v>0.32272000000000001</v>
@@ -1982,53 +1979,53 @@
       <c r="E30" s="6">
         <v>0.1678</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="13">
         <v>0.1128</v>
       </c>
-      <c r="G30" s="15">
+      <c r="G30" s="14">
         <v>5.5E-2</v>
       </c>
       <c r="H30" s="5"/>
-      <c r="I30" s="9">
+      <c r="I30" s="8">
         <v>46052.063148148147</v>
       </c>
-      <c r="J30" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B31" s="8">
+      <c r="J30" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A31" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" s="7">
         <v>0.36152000000000001</v>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="7">
         <v>1920969</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="7">
         <v>8.7980000000000003E-2</v>
       </c>
-      <c r="E31" s="8">
+      <c r="E31" s="7">
         <v>0.16963</v>
       </c>
-      <c r="F31" s="18">
+      <c r="F31" s="17">
         <v>0.1137</v>
       </c>
-      <c r="G31" s="19">
+      <c r="G31" s="18">
         <v>5.5899999999999998E-2</v>
       </c>
       <c r="H31" s="5"/>
-      <c r="I31" s="9">
+      <c r="I31" s="8">
         <v>46052.084803240738</v>
       </c>
-      <c r="J31" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A32" s="11" t="s">
-        <v>22</v>
+      <c r="J31" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="B32" s="6">
         <v>0.26854</v>
@@ -2042,53 +2039,53 @@
       <c r="E32" s="6">
         <v>3.0937000000000001</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="13">
         <v>2.7654000000000001</v>
       </c>
-      <c r="G32" s="15">
+      <c r="G32" s="14">
         <v>0.32829999999999998</v>
       </c>
       <c r="H32" s="5"/>
-      <c r="I32" s="9">
+      <c r="I32" s="8">
         <v>46052.106215277781</v>
       </c>
-      <c r="J32" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B33" s="8">
+      <c r="J32" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A33" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" s="7">
         <v>0.21840000000000001</v>
       </c>
-      <c r="C33" s="8">
+      <c r="C33" s="7">
         <v>21259871</v>
       </c>
-      <c r="D33" s="8">
+      <c r="D33" s="7">
         <v>0.97370000000000001</v>
       </c>
-      <c r="E33" s="8">
+      <c r="E33" s="7">
         <v>3.1073</v>
       </c>
-      <c r="F33" s="18">
+      <c r="F33" s="17">
         <v>2.7732999999999999</v>
       </c>
-      <c r="G33" s="19">
+      <c r="G33" s="18">
         <v>0.33400000000000002</v>
       </c>
       <c r="H33" s="5"/>
-      <c r="I33" s="9">
+      <c r="I33" s="8">
         <v>46052.127870370372</v>
       </c>
-      <c r="J33" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A34" s="11" t="s">
-        <v>23</v>
+      <c r="J33" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="10" t="s">
+        <v>21</v>
       </c>
       <c r="B34" s="6">
         <v>0.30059999999999998</v>
@@ -2102,112 +2099,112 @@
       <c r="E34" s="6">
         <v>0.23144999999999999</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F34" s="13">
         <v>0.15690000000000001</v>
       </c>
-      <c r="G34" s="15">
+      <c r="G34" s="14">
         <v>7.4499999999999997E-2</v>
       </c>
       <c r="H34" s="5"/>
-      <c r="I34" s="9">
+      <c r="I34" s="8">
         <v>46052.149305555555</v>
       </c>
-      <c r="J34" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B35" s="8">
+      <c r="J34" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A35" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B35" s="7">
         <v>0.28871999999999998</v>
       </c>
-      <c r="C35" s="8">
+      <c r="C35" s="7">
         <v>2100427</v>
       </c>
-      <c r="D35" s="8">
+      <c r="D35" s="7">
         <v>9.6199999999999994E-2</v>
       </c>
-      <c r="E35" s="8">
+      <c r="E35" s="7">
         <v>0.23224</v>
       </c>
-      <c r="F35" s="18">
+      <c r="F35" s="17">
         <v>0.15659999999999999</v>
       </c>
-      <c r="G35" s="19">
+      <c r="G35" s="18">
         <v>7.5600000000000001E-2</v>
       </c>
       <c r="H35" s="5"/>
-      <c r="I35" s="9">
+      <c r="I35" s="8">
         <v>46052.170960648145</v>
       </c>
-      <c r="J35" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A36" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B36" s="7">
+      <c r="J35" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36" s="5">
         <v>0.26927000000000001</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C36" s="5">
         <v>26172069</v>
       </c>
-      <c r="D36" s="7">
+      <c r="D36" s="5">
         <v>1.1987000000000001</v>
       </c>
-      <c r="E36" s="7">
+      <c r="E36" s="5">
         <v>3.1025999999999998</v>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="15">
         <v>2.7338</v>
       </c>
-      <c r="G36" s="17">
+      <c r="G36" s="16">
         <v>0.36880000000000002</v>
       </c>
       <c r="H36" s="5"/>
-      <c r="I36" s="9">
+      <c r="I36" s="8">
         <v>46052.192407407405</v>
       </c>
-      <c r="J36" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B37" s="7">
+      <c r="J36" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A37" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" s="5">
         <v>0.27557999999999999</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37" s="5">
         <v>26843030</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="5">
         <v>1.2294</v>
       </c>
-      <c r="E37" s="7">
+      <c r="E37" s="5">
         <v>3.1093000000000002</v>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="15">
         <v>2.7355999999999998</v>
       </c>
-      <c r="G37" s="17">
+      <c r="G37" s="16">
         <v>0.37369999999999998</v>
       </c>
       <c r="H37" s="5"/>
-      <c r="I37" s="9">
+      <c r="I37" s="8">
         <v>46052.213935185187</v>
       </c>
-      <c r="J37" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A38" s="11" t="s">
+      <c r="J37" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="10" t="s">
         <v>9</v>
       </c>
       <c r="B38" s="6">
@@ -2222,476 +2219,476 @@
       <c r="E38" s="6">
         <v>12.005000000000001</v>
       </c>
-      <c r="F38" s="14">
+      <c r="F38" s="13">
         <v>3.3099999999999997E-2</v>
       </c>
-      <c r="G38" s="15">
+      <c r="G38" s="14">
         <v>11.972</v>
       </c>
       <c r="H38" s="5"/>
-      <c r="I38" s="9">
+      <c r="I38" s="8">
         <v>46052.235590277778</v>
       </c>
-      <c r="J38" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A39" s="12" t="s">
+      <c r="J38" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B39" s="7">
+      <c r="B39" s="5">
         <v>3.6519999999999997E-2</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C39" s="5">
         <v>1173447</v>
       </c>
-      <c r="D39" s="7">
+      <c r="D39" s="5">
         <v>5.3744E-2</v>
       </c>
-      <c r="E39" s="7">
+      <c r="E39" s="5">
         <v>1.0257000000000001</v>
       </c>
-      <c r="F39" s="16">
+      <c r="F39" s="15">
         <v>2.9600000000000001E-2</v>
       </c>
-      <c r="G39" s="17">
+      <c r="G39" s="16">
         <v>0.996</v>
       </c>
       <c r="H39" s="5"/>
-      <c r="I39" s="9">
+      <c r="I39" s="8">
         <v>46052.257013888891</v>
       </c>
-      <c r="J39" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="13" t="s">
+      <c r="J39" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A40" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B40" s="8">
+      <c r="B40" s="7">
         <v>3.0419999999999999E-2</v>
       </c>
-      <c r="C40" s="8">
+      <c r="C40" s="7">
         <v>11440571</v>
       </c>
-      <c r="D40" s="8">
+      <c r="D40" s="7">
         <v>0.52398</v>
       </c>
-      <c r="E40" s="8">
+      <c r="E40" s="7">
         <v>12.005000000000001</v>
       </c>
-      <c r="F40" s="18">
+      <c r="F40" s="17">
         <v>2.5100000000000001E-2</v>
       </c>
-      <c r="G40" s="19">
+      <c r="G40" s="18">
         <v>11.98</v>
       </c>
       <c r="H40" s="5"/>
-      <c r="I40" s="9">
+      <c r="I40" s="8">
         <v>46052.278680555559</v>
       </c>
-      <c r="J40" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J40" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10">
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10">
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10">
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10">
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10">
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10">
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10">
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
     </row>
-    <row r="49" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="5:7">
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
     </row>
-    <row r="50" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="5:7">
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
     </row>
-    <row r="51" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="5:7">
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
     </row>
-    <row r="52" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="5:7">
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
     </row>
-    <row r="53" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="5:7">
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
     </row>
-    <row r="54" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="5:7">
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
     </row>
-    <row r="55" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="5:7">
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
     </row>
-    <row r="56" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="5:7">
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
     </row>
-    <row r="57" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="5:7">
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
     </row>
-    <row r="58" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="5:7">
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3"/>
     </row>
-    <row r="59" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="5:7">
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
     </row>
-    <row r="60" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="5:7">
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3"/>
     </row>
-    <row r="61" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="5:7">
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
     </row>
-    <row r="62" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="5:7">
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
     </row>
-    <row r="63" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="5:7">
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
     </row>
-    <row r="64" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="5:7">
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3"/>
     </row>
-    <row r="65" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="5:7">
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
       <c r="G65" s="3"/>
     </row>
-    <row r="66" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="5:7">
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
     </row>
-    <row r="67" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="5:7">
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
     </row>
-    <row r="68" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="5:7">
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
     </row>
-    <row r="69" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="5:7">
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
     </row>
-    <row r="70" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="5:7">
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
     </row>
-    <row r="71" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="5:7">
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
     </row>
-    <row r="72" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="5:7">
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
     </row>
-    <row r="73" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="5:7">
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="3"/>
     </row>
-    <row r="74" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="5:7">
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
     </row>
-    <row r="75" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="5:7">
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
       <c r="G75" s="3"/>
     </row>
-    <row r="76" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="5:7">
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="3"/>
     </row>
-    <row r="77" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="5:7">
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3"/>
     </row>
-    <row r="78" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="5:7">
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
     </row>
-    <row r="79" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="5:7">
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
     </row>
-    <row r="80" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="5:7">
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
     </row>
-    <row r="81" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="5:7">
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
     </row>
-    <row r="82" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="5:7">
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
     </row>
-    <row r="83" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="5:7">
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
     </row>
-    <row r="84" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="5:7">
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
     </row>
-    <row r="85" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="5:7">
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
       <c r="G85" s="3"/>
     </row>
-    <row r="86" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="5:7">
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
     </row>
-    <row r="87" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="5:7">
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
     </row>
-    <row r="88" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="5:7">
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
       <c r="G88" s="3"/>
     </row>
-    <row r="89" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="5:7">
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3"/>
     </row>
-    <row r="90" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="5:7">
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3"/>
     </row>
-    <row r="91" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="5:7">
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3"/>
     </row>
-    <row r="92" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="5:7">
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="3"/>
     </row>
-    <row r="93" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="5:7">
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="3"/>
     </row>
-    <row r="94" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="5:7">
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
       <c r="G94" s="3"/>
     </row>
-    <row r="95" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="5:7">
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3"/>
     </row>
-    <row r="96" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="5:7">
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
       <c r="G96" s="3"/>
     </row>
-    <row r="97" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="5:7">
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
       <c r="G97" s="3"/>
     </row>
-    <row r="98" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="5:7">
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
       <c r="G98" s="3"/>
     </row>
-    <row r="99" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="5:7">
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
       <c r="G99" s="3"/>
     </row>
-    <row r="100" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="5:7">
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
       <c r="G100" s="3"/>
     </row>
-    <row r="101" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="5:7">
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
       <c r="G101" s="3"/>
     </row>
-    <row r="102" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="5:7">
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
       <c r="G102" s="3"/>
     </row>
-    <row r="103" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="103" spans="5:7">
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
     </row>
-    <row r="104" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="104" spans="5:7">
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
     </row>
-    <row r="105" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="5:7">
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
     </row>
-    <row r="106" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="5:7">
       <c r="E106" s="3"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
     </row>
-    <row r="107" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="5:7">
       <c r="E107" s="3"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
     </row>
-    <row r="108" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="108" spans="5:7">
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
     </row>
-    <row r="109" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="109" spans="5:7">
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
       <c r="G109" s="3"/>
     </row>
-    <row r="110" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="110" spans="5:7">
       <c r="E110" s="3"/>
       <c r="F110" s="3"/>
       <c r="G110" s="3"/>
     </row>
-    <row r="111" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="111" spans="5:7">
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
       <c r="G111" s="3"/>
     </row>
-    <row r="112" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="5:7">
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
       <c r="G112" s="3"/>
     </row>
-    <row r="113" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="5:7">
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
       <c r="G113" s="3"/>
     </row>
-    <row r="114" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="5:7">
       <c r="E114" s="3"/>
       <c r="F114" s="3"/>
       <c r="G114" s="3"/>
     </row>
-    <row r="115" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="5:7">
       <c r="E115" s="3"/>
       <c r="F115" s="3"/>
       <c r="G115" s="3"/>
     </row>
-    <row r="116" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="5:7">
       <c r="E116" s="3"/>
       <c r="F116" s="3"/>
       <c r="G116" s="3"/>
     </row>
-    <row r="117" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="5:7">
       <c r="E117" s="3"/>
       <c r="F117" s="3"/>
       <c r="G117" s="3"/>
     </row>
-    <row r="118" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="5:7">
       <c r="E118" s="3"/>
       <c r="F118" s="3"/>
       <c r="G118" s="3"/>
     </row>
-    <row r="119" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="5:7">
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
       <c r="G119" s="3"/>
     </row>
-    <row r="120" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="5:7">
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
       <c r="G120" s="3"/>
@@ -2704,7 +2701,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2713,7 +2710,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
